--- a/outputs/gdp_projection_country_SSP2.xlsx
+++ b/outputs/gdp_projection_country_SSP2.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,432 +417,432 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ISO2</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>ISO3</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>OMNIA</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>2028</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>2029</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>2030</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>2031</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>2032</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>2033</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>2034</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>2035</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>2036</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>2037</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>2038</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>2039</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>2040</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>2041</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>2042</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>2043</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>2044</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>2045</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>2046</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>2047</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>2048</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>2049</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>2050</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>2051</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>2052</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>2053</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>2054</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>2055</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>2056</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>2057</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>2058</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>2059</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>2060</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>2061</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>2062</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>2063</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>2064</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>2065</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>2066</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>2067</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>2068</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>2069</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>2070</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>2071</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>2072</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>2073</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>2074</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>2075</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>2076</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>2077</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>2078</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>2079</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>2080</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>2081</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>2082</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>2083</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>2084</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>2085</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>2086</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>2087</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>2088</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>2089</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>2090</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>2091</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>2092</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>2093</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>2094</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>2095</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>2096</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>2097</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>2098</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>2099</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>2100</t>
         </is>
